--- a/tests/workbooktests/workbooks/test_capfloor.xlsx
+++ b/tests/workbooktests/workbooks/test_capfloor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310E900F-15C3-4A5E-AE87-CA79E41EF39C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA14B6CB-4671-476F-94B3-3A61A7F1E812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3210" yWindow="-20520" windowWidth="27315" windowHeight="17445" xr2:uid="{19136249-26FF-4BA6-AF5B-86DBDAF90384}"/>
+    <workbookView xWindow="3210" yWindow="-20520" windowWidth="27315" windowHeight="17445" activeTab="3" xr2:uid="{19136249-26FF-4BA6-AF5B-86DBDAF90384}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabs" sheetId="1" r:id="rId1"/>
@@ -23,17 +23,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -484,7 +473,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -500,9 +489,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -540,7 +529,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -646,7 +635,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -788,7 +777,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -797,15 +786,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68E6A32A-A0CE-401D-807A-F91DAD1693EF}">
   <dimension ref="B1:D7"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.109375" customWidth="1"/>
-    <col min="3" max="3" width="29.33203125" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="29.28515625" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
@@ -814,7 +803,7 @@
       </c>
       <c r="D2" s="27"/>
     </row>
-    <row r="3" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="25"/>
       <c r="C3" s="6" t="s">
         <v>6</v>
@@ -823,7 +812,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
@@ -834,7 +823,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
@@ -845,7 +834,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
@@ -856,7 +845,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
@@ -879,15 +868,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B7D6147-A96C-4CC0-B400-4E160714C85B}">
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.88671875" customWidth="1"/>
-    <col min="2" max="2" width="82.109375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" style="8" customWidth="1"/>
-    <col min="4" max="5" width="11.5546875" style="8"/>
+    <col min="1" max="1" width="57.85546875" customWidth="1"/>
+    <col min="2" max="2" width="82.140625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" style="8" customWidth="1"/>
+    <col min="4" max="5" width="11.5703125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -895,7 +884,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -904,7 +893,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
@@ -912,7 +901,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>11</v>
       </c>
@@ -920,7 +909,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
@@ -929,7 +918,7 @@
       </c>
       <c r="C6" s="7"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>13</v>
       </c>
@@ -937,7 +926,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>33</v>
       </c>
@@ -946,7 +935,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R8C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>34</v>
       </c>
@@ -955,7 +944,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R9C2USDLibor,A</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>15</v>
       </c>
@@ -964,14 +953,14 @@
         <v>欣[test_capfloor.xlsx]Cap!R10C2IborCoupon,A</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="28"/>
       <c r="B11" s="8" t="str">
         <f>_xll.qlIborCoupon(B6,B7,B4,B6,0,B9)</f>
         <v>欣[test_capfloor.xlsx]Cap!R11C2IborCoupon,A</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
         <v>35</v>
       </c>
@@ -979,13 +968,13 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="28"/>
       <c r="B13" s="8">
         <v>0.05</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>14</v>
       </c>
@@ -994,7 +983,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R14C2Cap,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>16</v>
       </c>
@@ -1003,7 +992,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R15C2CashFlow,A</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>18</v>
       </c>
@@ -1012,7 +1001,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>19</v>
       </c>
@@ -1021,7 +1010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>20</v>
       </c>
@@ -1030,7 +1019,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>21</v>
       </c>
@@ -1039,7 +1028,7 @@
         <v>46395</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>22</v>
       </c>
@@ -1048,7 +1037,7 @@
         <v>CAP</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>24</v>
       </c>
@@ -1057,7 +1046,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R21C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>23</v>
       </c>
@@ -1066,7 +1055,7 @@
         <v>3.0038607816972797E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>31</v>
       </c>
@@ -1075,7 +1064,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R23C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>32</v>
       </c>
@@ -1083,7 +1072,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -1092,7 +1081,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R25C2BlackCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>29</v>
       </c>
@@ -1101,7 +1090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1110,7 +1099,7 @@
         <v>5.119883118899232E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>17</v>
       </c>
@@ -1119,7 +1108,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>31</v>
       </c>
@@ -1128,7 +1117,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R29C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>36</v>
       </c>
@@ -1137,7 +1126,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R30C2OptionletVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>26</v>
       </c>
@@ -1146,7 +1135,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R31C2BlackCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>29</v>
       </c>
@@ -1155,7 +1144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -1164,7 +1153,7 @@
         <v>5.119883118899232E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>31</v>
       </c>
@@ -1173,7 +1162,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R34C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>32</v>
       </c>
@@ -1181,7 +1170,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -1190,7 +1179,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R36C2BachelierCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>29</v>
       </c>
@@ -1199,7 +1188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>30</v>
       </c>
@@ -1208,7 +1197,7 @@
         <v>5.119883118899232E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>31</v>
       </c>
@@ -1217,7 +1206,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R39C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>32</v>
       </c>
@@ -1226,7 +1215,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R40C2OptionletVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>28</v>
       </c>
@@ -1235,7 +1224,7 @@
         <v>欣[test_capfloor.xlsx]Cap!R41C2BachelierCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>29</v>
       </c>
@@ -1244,7 +1233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>30</v>
       </c>
@@ -1266,15 +1255,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12E17AF-C730-4393-B5FD-E373FB1E4DE1}">
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.88671875" customWidth="1"/>
-    <col min="2" max="2" width="82.109375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" style="8" customWidth="1"/>
-    <col min="4" max="5" width="11.5546875" style="8"/>
+    <col min="1" max="1" width="57.85546875" customWidth="1"/>
+    <col min="2" max="2" width="82.140625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" style="8" customWidth="1"/>
+    <col min="4" max="5" width="11.5703125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -1282,7 +1271,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1291,7 +1280,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
@@ -1299,7 +1288,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>11</v>
       </c>
@@ -1307,7 +1296,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
@@ -1316,7 +1305,7 @@
       </c>
       <c r="C6" s="7"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>13</v>
       </c>
@@ -1324,7 +1313,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>33</v>
       </c>
@@ -1333,7 +1322,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R8C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>34</v>
       </c>
@@ -1342,7 +1331,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R9C2USDLibor,A</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>15</v>
       </c>
@@ -1351,14 +1340,14 @@
         <v>欣[test_capfloor.xlsx]Floor!R10C2IborCoupon,A</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="28"/>
       <c r="B11" s="8" t="str">
         <f>_xll.qlIborCoupon(B6,B7,B4,B6,0,B9)</f>
         <v>欣[test_capfloor.xlsx]Floor!R11C2IborCoupon,A</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
         <v>37</v>
       </c>
@@ -1366,13 +1355,13 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="28"/>
       <c r="B13" s="8">
         <v>0.05</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>38</v>
       </c>
@@ -1381,7 +1370,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R14C2Floor,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>16</v>
       </c>
@@ -1390,7 +1379,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R15C2CashFlow,A</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>18</v>
       </c>
@@ -1399,7 +1388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>19</v>
       </c>
@@ -1408,7 +1397,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>20</v>
       </c>
@@ -1417,7 +1406,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>21</v>
       </c>
@@ -1426,7 +1415,7 @@
         <v>46395</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>22</v>
       </c>
@@ -1435,7 +1424,7 @@
         <v>FLOOR</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>24</v>
       </c>
@@ -1444,7 +1433,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R21C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>23</v>
       </c>
@@ -1453,7 +1442,7 @@
         <v>3.0038607816972797E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>31</v>
       </c>
@@ -1462,7 +1451,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R23C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>32</v>
       </c>
@@ -1470,7 +1459,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -1479,7 +1468,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R25C2BlackCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>29</v>
       </c>
@@ -1488,7 +1477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1497,7 +1486,7 @@
         <v>1.8800117125422198</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>17</v>
       </c>
@@ -1506,7 +1495,7 @@
         <v>9.9999999999999995E-8</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>31</v>
       </c>
@@ -1515,7 +1504,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R29C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>36</v>
       </c>
@@ -1524,7 +1513,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R30C2OptionletVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>26</v>
       </c>
@@ -1533,7 +1522,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R31C2BlackCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>29</v>
       </c>
@@ -1542,7 +1531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -1551,7 +1540,7 @@
         <v>1.8800117125422198</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>31</v>
       </c>
@@ -1560,7 +1549,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R34C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>32</v>
       </c>
@@ -1568,7 +1557,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -1577,7 +1566,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R36C2BachelierCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>29</v>
       </c>
@@ -1586,7 +1575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>30</v>
       </c>
@@ -1595,7 +1584,7 @@
         <v>1.8812663246588561</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>31</v>
       </c>
@@ -1604,7 +1593,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R39C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>32</v>
       </c>
@@ -1613,7 +1602,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R40C2OptionletVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>28</v>
       </c>
@@ -1622,7 +1611,7 @@
         <v>欣[test_capfloor.xlsx]Floor!R41C2BachelierCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>29</v>
       </c>
@@ -1631,7 +1620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>30</v>
       </c>
@@ -1653,15 +1642,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61CB6721-D4A1-4BF9-B717-72F271F45D15}">
   <dimension ref="A1:E45"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.88671875" customWidth="1"/>
-    <col min="2" max="2" width="82.109375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" style="8" customWidth="1"/>
-    <col min="4" max="5" width="11.5546875" style="8"/>
+    <col min="1" max="1" width="57.85546875" customWidth="1"/>
+    <col min="2" max="2" width="82.140625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" style="8" customWidth="1"/>
+    <col min="4" max="5" width="11.5703125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -1669,7 +1658,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1678,7 +1667,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
@@ -1686,7 +1675,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>11</v>
       </c>
@@ -1694,7 +1683,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
@@ -1703,7 +1692,7 @@
       </c>
       <c r="C6" s="7"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>13</v>
       </c>
@@ -1711,7 +1700,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>33</v>
       </c>
@@ -1720,7 +1709,7 @@
         <v>欣[test_capfloor.xlsx]Collar!R8C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>34</v>
       </c>
@@ -1729,23 +1718,23 @@
         <v>欣[test_capfloor.xlsx]Collar!R9C2USDLibor,A</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="8" t="str">
-        <f>_xll.qlIborCoupon(B4,B5,B2,B4,0,B9,,,,,,,,B2)</f>
+        <f>_xll.qlIborCoupon(B4,B5,B2,B4,0,B9,,,,,,,,,B2)</f>
         <v>欣[test_capfloor.xlsx]Collar!R10C2IborCoupon,A</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="28"/>
       <c r="B11" s="8" t="str">
-        <f>_xll.qlIborCoupon(B6,B7,B4,B6,0,B9,,,,,,,,B2)</f>
+        <f>_xll.qlIborCoupon(B6,B7,B4,B6,0,B9,,,,,,,,,B2)</f>
         <v>欣[test_capfloor.xlsx]Collar!R11C2IborCoupon,A</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
         <v>35</v>
       </c>
@@ -1753,13 +1742,13 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28"/>
       <c r="B13" s="8">
         <v>0.05</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
         <v>37</v>
       </c>
@@ -1767,13 +1756,13 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
       <c r="B15" s="8">
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>39</v>
       </c>
@@ -1782,7 +1771,7 @@
         <v>欣[test_capfloor.xlsx]Collar!R16C2Collar,A</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>16</v>
       </c>
@@ -1791,7 +1780,7 @@
         <v>欣[test_capfloor.xlsx]Collar!R17C2CashFlow,A</v>
       </c>
     </row>
-    <row r="18" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>18</v>
       </c>
@@ -1800,7 +1789,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>19</v>
       </c>
@@ -1809,7 +1798,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>20</v>
       </c>
@@ -1818,7 +1807,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>21</v>
       </c>
@@ -1827,7 +1816,7 @@
         <v>46395</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>22</v>
       </c>
@@ -1836,7 +1825,7 @@
         <v>COLLAR</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>24</v>
       </c>
@@ -1845,16 +1834,16 @@
         <v>欣[test_capfloor.xlsx]Collar!R23C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="8">
         <f>_xll.qlCapFloorAtmRate(B16,B23)</f>
-        <v>3.0038607816972797E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+        <v>3.00386078169728E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>31</v>
       </c>
@@ -1863,7 +1852,7 @@
         <v>欣[test_capfloor.xlsx]Collar!R25C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>32</v>
       </c>
@@ -1871,7 +1860,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="27" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -1880,7 +1869,7 @@
         <v>欣[test_capfloor.xlsx]Collar!R27C2BlackCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="28" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>29</v>
       </c>
@@ -1889,25 +1878,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
       <c r="B29" s="8">
         <f>_xll.qlInstrumentNPV(B16,B28)</f>
-        <v>5.1198820569102951E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+        <v>3.9189553217390954E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B30" s="8">
         <f>_xll.qlCapFloorImpliedVolatility(B16,B29,B25,0.2)</f>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+        <v>9.9999999999999995E-8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>31</v>
       </c>
@@ -1916,7 +1905,7 @@
         <v>欣[test_capfloor.xlsx]Collar!R31C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="32" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>36</v>
       </c>
@@ -1925,7 +1914,7 @@
         <v>欣[test_capfloor.xlsx]Collar!R32C2OptionletVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="33" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>26</v>
       </c>
@@ -1934,7 +1923,7 @@
         <v>欣[test_capfloor.xlsx]Collar!R33C2BlackCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="34" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>29</v>
       </c>
@@ -1943,16 +1932,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="8">
         <f>_xll.qlInstrumentNPV(B16,B34)</f>
-        <v>5.1198820569102951E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+        <v>3.9189553217390954E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>31</v>
       </c>
@@ -1961,7 +1950,7 @@
         <v>欣[test_capfloor.xlsx]Collar!R36C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="37" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>32</v>
       </c>
@@ -1969,7 +1958,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>27</v>
       </c>
@@ -1978,7 +1967,7 @@
         <v>欣[test_capfloor.xlsx]Collar!R38C2BachelierCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="39" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>29</v>
       </c>
@@ -1987,16 +1976,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>30</v>
       </c>
       <c r="B40" s="8">
         <f>_xll.qlInstrumentNPV(B16,B39)</f>
-        <v>3.8652710022632174E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+        <v>3.9189553217390954E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
         <v>31</v>
       </c>
@@ -2005,7 +1994,7 @@
         <v>欣[test_capfloor.xlsx]Collar!R41C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="42" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
         <v>32</v>
       </c>
@@ -2014,7 +2003,7 @@
         <v>欣[test_capfloor.xlsx]Collar!R42C2OptionletVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="43" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>28</v>
       </c>
@@ -2023,7 +2012,7 @@
         <v>欣[test_capfloor.xlsx]Collar!R43C2BachelierCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="44" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
         <v>29</v>
       </c>
@@ -2032,13 +2021,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>30</v>
       </c>
       <c r="B45" s="8">
         <f>_xll.qlInstrumentNPV(B16,B44)</f>
-        <v>3.8652710022632174E-3</v>
+        <v>3.9189553217390954E-3</v>
       </c>
     </row>
   </sheetData>
@@ -2055,15 +2044,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A1DD47-423E-4B71-9770-A17F281B15D1}">
   <dimension ref="A1:E51"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.88671875" customWidth="1"/>
-    <col min="2" max="2" width="55.88671875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" style="8" customWidth="1"/>
-    <col min="4" max="5" width="11.5546875" style="8"/>
+    <col min="1" max="1" width="57.85546875" customWidth="1"/>
+    <col min="2" max="2" width="55.85546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" style="8" customWidth="1"/>
+    <col min="4" max="5" width="11.5703125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2071,7 +2060,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2080,7 +2069,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -2088,7 +2077,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2096,7 +2085,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>33</v>
       </c>
@@ -2105,7 +2094,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R6C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>42</v>
       </c>
@@ -2114,7 +2103,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R7C2USDLibor,A</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -2122,7 +2111,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -2130,7 +2119,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -2138,13 +2127,13 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
         <v>46</v>
       </c>
       <c r="B11" s="7"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -2152,7 +2141,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -2160,7 +2149,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -2168,7 +2157,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>50</v>
       </c>
@@ -2176,7 +2165,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>51</v>
       </c>
@@ -2184,19 +2173,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>52</v>
       </c>
       <c r="B17" s="7"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>53</v>
       </c>
       <c r="B18" s="7"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -2204,7 +2193,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -2212,12 +2201,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>61</v>
       </c>
@@ -2226,7 +2215,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R22C2CapFloor,A</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>16</v>
       </c>
@@ -2235,7 +2224,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R23C2CashFlow,A</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>18</v>
       </c>
@@ -2244,7 +2233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>19</v>
       </c>
@@ -2253,7 +2242,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>20</v>
       </c>
@@ -2262,7 +2251,7 @@
         <v>45670</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>21</v>
       </c>
@@ -2271,7 +2260,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>22</v>
       </c>
@@ -2280,7 +2269,7 @@
         <v>FLOOR</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>24</v>
       </c>
@@ -2289,7 +2278,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R29C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>23</v>
       </c>
@@ -2298,7 +2287,7 @@
         <v>2.9700276978901811E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>31</v>
       </c>
@@ -2307,7 +2296,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R31C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>32</v>
       </c>
@@ -2315,7 +2304,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>25</v>
       </c>
@@ -2324,7 +2313,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R33C2BlackCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>29</v>
       </c>
@@ -2333,7 +2322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>30</v>
       </c>
@@ -2342,7 +2331,7 @@
         <v>4.633076994730075E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>17</v>
       </c>
@@ -2351,7 +2340,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>31</v>
       </c>
@@ -2360,7 +2349,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R37C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>36</v>
       </c>
@@ -2369,7 +2358,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R38C2OptionletVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>26</v>
       </c>
@@ -2378,7 +2367,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R39C2BlackCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>29</v>
       </c>
@@ -2387,7 +2376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>30</v>
       </c>
@@ -2396,7 +2385,7 @@
         <v>1.339625003165777</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
         <v>31</v>
       </c>
@@ -2405,7 +2394,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R42C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>32</v>
       </c>
@@ -2413,7 +2402,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>27</v>
       </c>
@@ -2422,7 +2411,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R44C2BachelierCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
         <v>29</v>
       </c>
@@ -2431,7 +2420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>30</v>
       </c>
@@ -2440,7 +2429,7 @@
         <v>0.48196197214187886</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>31</v>
       </c>
@@ -2449,7 +2438,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R47C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>36</v>
       </c>
@@ -2458,7 +2447,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R48C2OptionletVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
         <v>28</v>
       </c>
@@ -2467,7 +2456,7 @@
         <v>欣[test_capfloor.xlsx]MakeCapFloor!R49C2BachelierCapFloorEngine,A</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>29</v>
       </c>
@@ -2476,7 +2465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>30</v>
       </c>
